--- a/data/AttributeAutoPlan.xlsx
+++ b/data/AttributeAutoPlan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,30 +493,12 @@
       <c r="D6" t="n">
         <v>103</v>
       </c>
-      <c r="E6" t="n">
-        <v>101</v>
-      </c>
-      <c r="F6" t="n">
-        <v>104</v>
-      </c>
-      <c r="G6" t="n">
-        <v>102</v>
-      </c>
       <c r="I6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>通用:力量为主,体质/敏捷辅</t>
+          <t>通用:全投力量(集中投资公式下分散投比满投少约 9% 有效点)</t>
         </is>
       </c>
     </row>
@@ -595,24 +577,12 @@
       <c r="D9" t="n">
         <v>103</v>
       </c>
-      <c r="E9" t="n">
-        <v>104</v>
-      </c>
-      <c r="F9" t="n">
-        <v>101</v>
-      </c>
       <c r="I9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>物理:力量 4 敏捷 1 体质 1</t>
+          <t>破军:全投力量(物伤 +30%)</t>
         </is>
       </c>
     </row>
@@ -691,24 +661,12 @@
       <c r="D12" t="n">
         <v>102</v>
       </c>
-      <c r="E12" t="n">
-        <v>101</v>
-      </c>
-      <c r="F12" t="n">
-        <v>104</v>
-      </c>
       <c r="I12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
         <v>1</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>法系:灵力 4 体质 1 敏捷 1</t>
+          <t>玄霄:全投灵力(法伤 +27% / 法力 +15%)</t>
         </is>
       </c>
     </row>
@@ -805,6 +763,50 @@
       <c r="N15" t="inlineStr">
         <is>
           <t>宝宝通用:力量为主、体质次之、敏捷补(核心线宝宝只普攻,不投灵力)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>31</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>101</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>丹心:全投体质(气血 +25% / 防御 +12%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>41</v>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>104</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>逐风:全投敏捷(速度 +20%)</t>
         </is>
       </c>
     </row>

--- a/data/AttributeAutoPlan.xlsx
+++ b/data/AttributeAutoPlan.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,307 +504,121 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>205</v>
-      </c>
-      <c r="E7" t="n">
-        <v>204</v>
-      </c>
-      <c r="F7" t="n">
-        <v>202</v>
+        <v>103</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>通用:先满土、再满火、后加木</t>
+          <t>破军:全投力量(物伤 +30%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>303</v>
-      </c>
-      <c r="E8" t="n">
-        <v>304</v>
+        <v>102</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" t="n">
         <v>1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>通用:魔攻为主</t>
+          <t>玄霄:全投灵力(法伤 +27% / 法力 +15%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>103</v>
+        <v>403</v>
+      </c>
+      <c r="E9" t="n">
+        <v>401</v>
+      </c>
+      <c r="F9" t="n">
+        <v>404</v>
       </c>
       <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>破军:全投力量(物伤 +30%)</t>
+          <t>宝宝通用:力量为主、体质次之、敏捷补(核心线宝宝只普攻,不投灵力)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
-      </c>
-      <c r="E10" t="n">
-        <v>204</v>
-      </c>
-      <c r="F10" t="n">
-        <v>202</v>
+        <v>101</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>物理:先满土、再满火、后加木</t>
+          <t>丹心:全投体质(气血 +25% / 防御 +12%)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>303</v>
-      </c>
-      <c r="E11" t="n">
-        <v>304</v>
+        <v>104</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="N11" t="inlineStr">
-        <is>
-          <t>物理:魔攻为主</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>21</v>
-      </c>
-      <c r="B12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="n">
-        <v>102</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>玄霄:全投灵力(法伤 +27% / 法力 +15%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>22</v>
-      </c>
-      <c r="B13" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>201</v>
-      </c>
-      <c r="E13" t="n">
-        <v>204</v>
-      </c>
-      <c r="F13" t="n">
-        <v>202</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>法系:先满金、再满火、后加木</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>23</v>
-      </c>
-      <c r="B14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" t="n">
-        <v>301</v>
-      </c>
-      <c r="E14" t="n">
-        <v>302</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>法系:仙攻为主</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>4</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>403</v>
-      </c>
-      <c r="E15" t="n">
-        <v>401</v>
-      </c>
-      <c r="F15" t="n">
-        <v>404</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>宝宝通用:力量为主、体质次之、敏捷补(核心线宝宝只普攻,不投灵力)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>31</v>
-      </c>
-      <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>101</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>丹心:全投体质(气血 +25% / 防御 +12%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>41</v>
-      </c>
-      <c r="B17" t="n">
-        <v>4</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>104</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="inlineStr">
         <is>
           <t>逐风:全投敏捷(速度 +20%)</t>
         </is>

--- a/data/AttributeAutoPlan.xlsx
+++ b/data/AttributeAutoPlan.xlsx
@@ -493,12 +493,18 @@
       <c r="D6" t="n">
         <v>103</v>
       </c>
-      <c r="I6" t="n">
+      <c r="E6">
+        <v>101</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
         <v>1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>通用:全投力量(集中投资公式下分散投比满投少约 9% 有效点)</t>
+          <t>通用：4力1体，兼顾伤害与生存</t>
         </is>
       </c>
     </row>
@@ -515,12 +521,18 @@
       <c r="D7" t="n">
         <v>103</v>
       </c>
-      <c r="I7" t="n">
+      <c r="E7">
+        <v>101</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7">
         <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>破军:全投力量(物伤 +30%)</t>
+          <t>破军：4力1体，物理输出兼顾生存</t>
         </is>
       </c>
     </row>
@@ -537,12 +549,18 @@
       <c r="D8" t="n">
         <v>102</v>
       </c>
-      <c r="I8" t="n">
+      <c r="E8">
+        <v>101</v>
+      </c>
+      <c r="I8">
+        <v>4</v>
+      </c>
+      <c r="J8">
         <v>1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>玄霄:全投灵力(法伤 +27% / 法力 +15%)</t>
+          <t>玄霄：4灵1体，法术输出兼顾生存</t>
         </is>
       </c>
     </row>
@@ -590,15 +608,27 @@
       <c r="C10" t="n">
         <v>1</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
+        <v>102</v>
+      </c>
+      <c r="E10">
         <v>101</v>
       </c>
-      <c r="I10" t="n">
+      <c r="F10">
+        <v>104</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>2</v>
+      </c>
+      <c r="K10">
         <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>丹心:全投体质(气血 +25% / 防御 +12%)</t>
+          <t>丹心：2灵2体1敏，兼顾治疗、生存与出手</t>
         </is>
       </c>
     </row>
@@ -615,12 +645,24 @@
       <c r="D11" t="n">
         <v>104</v>
       </c>
-      <c r="I11" t="n">
+      <c r="E11">
+        <v>101</v>
+      </c>
+      <c r="F11">
+        <v>103</v>
+      </c>
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
         <v>1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>逐风:全投敏捷(速度 +20%)</t>
+          <t>逐风：3敏1体1力，抢速并保留生存与输出</t>
         </is>
       </c>
     </row>
